--- a/artfynd/A 48896-2022 artfynd.xlsx
+++ b/artfynd/A 48896-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48896-2022 artfynd.xlsx
+++ b/artfynd/A 48896-2022 artfynd.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agneta Sundkvist, Hans Andersson</t>
+          <t>Hans Andersson, Agneta Sundkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 48896-2022 artfynd.xlsx
+++ b/artfynd/A 48896-2022 artfynd.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Andersson, Agneta Sundkvist</t>
+          <t>Agneta Sundkvist, Hans Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 48896-2022 artfynd.xlsx
+++ b/artfynd/A 48896-2022 artfynd.xlsx
@@ -1078,7 +1078,7 @@
         <v>125712459</v>
       </c>
       <c r="B5" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 48896-2022 artfynd.xlsx
+++ b/artfynd/A 48896-2022 artfynd.xlsx
@@ -1078,7 +1078,7 @@
         <v>125712459</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
